--- a/tools/importer/reports/import-hey-conad.report.xlsx
+++ b/tools/importer/reports/import-hey-conad.report.xlsx
@@ -49,7 +49,7 @@
     <t>success</t>
   </si>
   <si>
-    <t>2026-05-25T19:04:46.614Z</t>
+    <t>2026-05-26T16:22:30.228Z</t>
   </si>
   <si>
     <t>Hey Conad | Scarica l’App | Acquista Online i nostri Servizi Digitali | Conad</t>

--- a/tools/importer/reports/import-hey-conad.report.xlsx
+++ b/tools/importer/reports/import-hey-conad.report.xlsx
@@ -49,7 +49,7 @@
     <t>success</t>
   </si>
   <si>
-    <t>2026-05-26T16:22:30.228Z</t>
+    <t>2026-05-26T16:32:37.397Z</t>
   </si>
   <si>
     <t>Hey Conad | Scarica l’App | Acquista Online i nostri Servizi Digitali | Conad</t>

--- a/tools/importer/reports/import-hey-conad.report.xlsx
+++ b/tools/importer/reports/import-hey-conad.report.xlsx
@@ -40,7 +40,7 @@
     <t>hey-conad.report.json</t>
   </si>
   <si>
-    <t>["hero-landing","columns-banner","columns-service","columns-service","columns-service","columns-service"]</t>
+    <t>["hero-landing","columns-banner","promo-card","promo-card","promo-card","promo-card"]</t>
   </si>
   <si>
     <t>hey-conad</t>
@@ -49,7 +49,7 @@
     <t>success</t>
   </si>
   <si>
-    <t>2026-05-26T16:32:37.397Z</t>
+    <t>2026-05-26T16:43:04.041Z</t>
   </si>
   <si>
     <t>Hey Conad | Scarica l’App | Acquista Online i nostri Servizi Digitali | Conad</t>

--- a/tools/importer/reports/import-hey-conad.report.xlsx
+++ b/tools/importer/reports/import-hey-conad.report.xlsx
@@ -40,7 +40,7 @@
     <t>hey-conad.report.json</t>
   </si>
   <si>
-    <t>["hero-landing","columns-banner","promo-card","promo-card","promo-card","promo-card"]</t>
+    <t>["hero-landing","cta-banner","promo-card","promo-card","promo-card","promo-card"]</t>
   </si>
   <si>
     <t>hey-conad</t>
@@ -49,7 +49,7 @@
     <t>success</t>
   </si>
   <si>
-    <t>2026-05-26T16:43:04.041Z</t>
+    <t>2026-05-26T17:11:32.759Z</t>
   </si>
   <si>
     <t>Hey Conad | Scarica l’App | Acquista Online i nostri Servizi Digitali | Conad</t>

--- a/tools/importer/reports/import-hey-conad.report.xlsx
+++ b/tools/importer/reports/import-hey-conad.report.xlsx
@@ -49,7 +49,7 @@
     <t>success</t>
   </si>
   <si>
-    <t>2026-05-26T17:11:32.759Z</t>
+    <t>2026-05-26T17:30:43.410Z</t>
   </si>
   <si>
     <t>Hey Conad | Scarica l’App | Acquista Online i nostri Servizi Digitali | Conad</t>

--- a/tools/importer/reports/import-hey-conad.report.xlsx
+++ b/tools/importer/reports/import-hey-conad.report.xlsx
@@ -49,7 +49,7 @@
     <t>success</t>
   </si>
   <si>
-    <t>2026-05-26T17:30:43.410Z</t>
+    <t>2026-05-26T17:38:06.871Z</t>
   </si>
   <si>
     <t>Hey Conad | Scarica l’App | Acquista Online i nostri Servizi Digitali | Conad</t>
